--- a/PlanDist.xlsx
+++ b/PlanDist.xlsx
@@ -4,7 +4,7 @@
   <workbookPr codeName="EstaPastaDeTrabalho"/>
   <workbookProtection lockStructure="1" workbookAlgorithmName="SHA-512" workbookHashValue="kGF/CmRvAYvYFio2rKevaoVoOEuDsD9aA1iepPWm9hrpOlqPcLeuMqXgUtPnrYkyjE2rwubht0jFgVIX7Y7Dww==" workbookSaltValue="1HcCVsKxrOJYRcjmNwaQYg==" workbookSpinCount="100000"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="1" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="1" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="PARÂMETROS" sheetId="1" state="hidden" r:id="rId1"/>
@@ -788,13 +788,21 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="4" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="1" hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -803,6 +811,14 @@
     <xf numFmtId="0" fontId="11" fillId="7" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="1" hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -820,31 +836,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="1" hidden="1"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="4" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
     <xf numFmtId="164" fontId="21" fillId="12" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -857,11 +848,20 @@
     <xf numFmtId="0" fontId="24" fillId="13" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1356,25 +1356,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R403"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col hidden="1" width="24.140625" customWidth="1" style="13" min="1" max="1"/>
-    <col width="1.42578125" customWidth="1" style="1" min="2" max="2"/>
-    <col width="20.7109375" customWidth="1" style="1" min="3" max="3"/>
-    <col width="13.5703125" customWidth="1" style="1" min="4" max="4"/>
+    <col hidden="1" width="24.109375" customWidth="1" style="13" min="1" max="1"/>
+    <col width="1.44140625" customWidth="1" style="1" min="2" max="2"/>
+    <col width="20.6640625" customWidth="1" style="1" min="3" max="3"/>
+    <col width="13.5546875" customWidth="1" style="1" min="4" max="4"/>
     <col width="52" customWidth="1" style="1" min="5" max="5"/>
     <col width="15" customWidth="1" style="1" min="6" max="6"/>
-    <col width="15.42578125" customWidth="1" style="1" min="7" max="8"/>
-    <col width="18.42578125" customWidth="1" style="1" min="9" max="9"/>
-    <col width="1.42578125" customWidth="1" style="1" min="10" max="10"/>
-    <col width="25.85546875" customWidth="1" style="1" min="11" max="11"/>
-    <col width="1.42578125" customWidth="1" style="1" min="12" max="12"/>
-    <col width="25.42578125" customWidth="1" style="1" min="13" max="13"/>
-    <col width="1.42578125" customWidth="1" style="1" min="14" max="14"/>
-    <col width="17.140625" customWidth="1" style="1" min="15" max="15"/>
-    <col width="9.140625" customWidth="1" style="1" min="16" max="16"/>
-    <col width="28.28515625" customWidth="1" style="1" min="17" max="18"/>
-    <col width="9.140625" customWidth="1" style="1" min="19" max="16384"/>
+    <col width="15.44140625" customWidth="1" style="1" min="7" max="8"/>
+    <col width="18.44140625" customWidth="1" style="1" min="9" max="9"/>
+    <col width="1.44140625" customWidth="1" style="1" min="10" max="10"/>
+    <col width="25.88671875" customWidth="1" style="1" min="11" max="11"/>
+    <col width="1.44140625" customWidth="1" style="1" min="12" max="12"/>
+    <col width="25.44140625" customWidth="1" style="1" min="13" max="13"/>
+    <col width="1.44140625" customWidth="1" style="1" min="14" max="14"/>
+    <col width="17.109375" customWidth="1" style="1" min="15" max="15"/>
+    <col width="9.109375" customWidth="1" style="1" min="16" max="16"/>
+    <col width="28.33203125" customWidth="1" style="1" min="17" max="18"/>
+    <col width="9.109375" customWidth="1" style="1" min="19" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="53.25" customHeight="1">
@@ -1396,7 +1396,7 @@
       <c r="N1" s="107" t="n"/>
       <c r="O1" s="108" t="n"/>
     </row>
-    <row r="3" ht="30" customHeight="1">
+    <row r="3" ht="28.8" customHeight="1">
       <c r="A3" s="15" t="inlineStr">
         <is>
           <t>COD.</t>
@@ -3616,7 +3616,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="30" customHeight="1">
+    <row r="69" ht="28.8" customHeight="1">
       <c r="A69" s="15">
         <f>C69&amp;D69</f>
         <v/>
@@ -4562,7 +4562,7 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="30" customHeight="1">
+    <row r="100" ht="28.8" customHeight="1">
       <c r="A100" s="15">
         <f>C100&amp;D100</f>
         <v/>
@@ -9827,48 +9827,48 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AX510"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col width="10.140625" customWidth="1" style="20" min="1" max="1"/>
-    <col width="17.28515625" customWidth="1" style="20" min="2" max="3"/>
+    <col width="10.109375" customWidth="1" style="20" min="1" max="1"/>
+    <col width="17.33203125" customWidth="1" style="20" min="2" max="3"/>
     <col width="56" customWidth="1" style="19" min="4" max="4"/>
-    <col width="14.5703125" customWidth="1" style="19" min="5" max="5"/>
-    <col width="66.28515625" customWidth="1" style="19" min="6" max="6"/>
-    <col width="34.28515625" customWidth="1" style="19" min="7" max="7"/>
-    <col width="22.7109375" customWidth="1" style="19" min="8" max="8"/>
-    <col width="21.140625" customWidth="1" style="19" min="9" max="9"/>
-    <col width="17.28515625" customWidth="1" style="19" min="10" max="11"/>
-    <col width="21.28515625" customWidth="1" style="19" min="12" max="12"/>
-    <col width="69.5703125" customWidth="1" style="19" min="13" max="13"/>
-    <col width="1.5703125" customWidth="1" style="19" min="14" max="14"/>
-    <col width="19.28515625" customWidth="1" style="19" min="15" max="15"/>
-    <col width="9.140625" customWidth="1" style="19" min="16" max="28"/>
-    <col width="9.140625" customWidth="1" style="19" min="29" max="29"/>
-    <col width="19.42578125" customWidth="1" style="19" min="30" max="30"/>
-    <col width="9.140625" customWidth="1" style="19" min="31" max="31"/>
-    <col width="19.42578125" customWidth="1" style="19" min="32" max="32"/>
-    <col width="111.5703125" customWidth="1" style="19" min="33" max="33"/>
-    <col width="20.28515625" customWidth="1" style="19" min="34" max="36"/>
-    <col width="16.42578125" customWidth="1" style="19" min="37" max="37"/>
-    <col width="9.140625" customWidth="1" style="19" min="38" max="40"/>
-    <col width="18.85546875" customWidth="1" style="19" min="41" max="41"/>
-    <col width="17.5703125" customWidth="1" style="19" min="42" max="42"/>
-    <col width="17.7109375" customWidth="1" style="19" min="43" max="43"/>
-    <col width="21.140625" customWidth="1" style="19" min="44" max="44"/>
-    <col width="2.7109375" customWidth="1" style="19" min="45" max="45"/>
-    <col width="16.42578125" customWidth="1" style="19" min="46" max="47"/>
-    <col width="2.7109375" customWidth="1" style="19" min="48" max="48"/>
-    <col width="14.5703125" customWidth="1" style="19" min="49" max="50"/>
-    <col width="9.140625" customWidth="1" style="19" min="51" max="51"/>
-    <col width="9.140625" customWidth="1" style="19" min="52" max="52"/>
-    <col width="9.140625" customWidth="1" style="19" min="53" max="16384"/>
+    <col width="14.5546875" customWidth="1" style="19" min="5" max="5"/>
+    <col width="66.33203125" customWidth="1" style="19" min="6" max="6"/>
+    <col width="34.33203125" customWidth="1" style="19" min="7" max="7"/>
+    <col width="22.6640625" customWidth="1" style="19" min="8" max="8"/>
+    <col width="21.109375" customWidth="1" style="19" min="9" max="9"/>
+    <col width="17.33203125" customWidth="1" style="19" min="10" max="11"/>
+    <col width="21.33203125" customWidth="1" style="19" min="12" max="12"/>
+    <col width="69.5546875" customWidth="1" style="19" min="13" max="13"/>
+    <col width="1.5546875" customWidth="1" style="19" min="14" max="14"/>
+    <col width="19.33203125" customWidth="1" style="19" min="15" max="15"/>
+    <col width="9.109375" customWidth="1" style="19" min="16" max="28"/>
+    <col width="9.109375" customWidth="1" style="19" min="29" max="29"/>
+    <col width="19.44140625" customWidth="1" style="19" min="30" max="30"/>
+    <col width="9.109375" customWidth="1" style="19" min="31" max="31"/>
+    <col width="19.44140625" customWidth="1" style="19" min="32" max="32"/>
+    <col width="111.5546875" customWidth="1" style="19" min="33" max="33"/>
+    <col width="20.33203125" customWidth="1" style="19" min="34" max="36"/>
+    <col width="16.44140625" customWidth="1" style="19" min="37" max="37"/>
+    <col width="9.109375" customWidth="1" style="19" min="38" max="40"/>
+    <col width="18.88671875" customWidth="1" style="19" min="41" max="41"/>
+    <col width="17.5546875" customWidth="1" style="19" min="42" max="42"/>
+    <col width="17.6640625" customWidth="1" style="19" min="43" max="43"/>
+    <col width="21.109375" customWidth="1" style="19" min="44" max="44"/>
+    <col width="2.6640625" customWidth="1" style="19" min="45" max="45"/>
+    <col width="16.44140625" customWidth="1" style="19" min="46" max="47"/>
+    <col width="2.6640625" customWidth="1" style="19" min="48" max="48"/>
+    <col width="14.5546875" customWidth="1" style="19" min="49" max="50"/>
+    <col width="9.109375" customWidth="1" style="19" min="51" max="51"/>
+    <col width="9.109375" customWidth="1" style="19" min="52" max="52"/>
+    <col width="9.109375" customWidth="1" style="19" min="53" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="62.25" customHeight="1">
       <c r="A1" s="18" t="n"/>
       <c r="B1" s="52" t="n"/>
       <c r="C1" s="56" t="n"/>
-      <c r="D1" s="93">
+      <c r="D1" s="97">
         <f>CONCATENATE("CTD ",C5," - Rev.: ",C6," - Composição de Valores - ",C8," - ",C4)</f>
         <v/>
       </c>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="I3" s="112" t="n"/>
       <c r="J3" s="60" t="n"/>
-      <c r="K3" s="90" t="inlineStr">
+      <c r="K3" s="94" t="inlineStr">
         <is>
           <t>Data da última atualização de valores:</t>
         </is>
@@ -9922,7 +9922,7 @@
       <c r="B4" s="112" t="n"/>
       <c r="C4" s="113" t="inlineStr">
         <is>
-          <t>Luan Araujo</t>
+          <t>Iago Rangel</t>
         </is>
       </c>
       <c r="D4" s="114" t="n"/>
@@ -9948,7 +9948,7 @@
       <c r="B5" s="112" t="n"/>
       <c r="C5" s="59" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="E5" s="21" t="n"/>
@@ -9957,7 +9957,7 @@
       <c r="H5" s="26" t="n"/>
       <c r="I5" s="23" t="n"/>
       <c r="J5" s="24" t="n"/>
-      <c r="K5" s="91">
+      <c r="K5" s="95">
         <f>AK11</f>
         <v/>
       </c>
@@ -9971,11 +9971,7 @@
         </is>
       </c>
       <c r="B6" s="112" t="n"/>
-      <c r="C6" s="58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="C6" s="58" t="inlineStr"/>
       <c r="E6" s="50" t="n"/>
       <c r="F6" s="21" t="n"/>
       <c r="G6" s="22" t="n"/>
@@ -10183,7 +10179,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="33" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C11" s="33" t="inlineStr">
         <is>
@@ -10192,7 +10188,7 @@
       </c>
       <c r="D11" s="33" t="inlineStr">
         <is>
-          <t>010 DIFUSOR ALS DS2 2000 C/ CAIXA PLENUM PH4 TROX</t>
+          <t>010 DAMPER RG-B 480x405 TROX</t>
         </is>
       </c>
       <c r="E11" s="33" t="inlineStr">
@@ -10206,20 +10202,20 @@
       </c>
       <c r="G11" s="33" t="inlineStr">
         <is>
-          <t>ALS-DS2-2000/K/A/198/0/PH4</t>
+          <t>RG-B-480x405/D/0/00/000</t>
         </is>
       </c>
       <c r="H11" s="33" t="n">
-        <v>76169900</v>
+        <v>90261029</v>
       </c>
       <c r="I11" s="34" t="n">
-        <v>595.02</v>
+        <v>176.23</v>
       </c>
       <c r="J11" s="35" t="n">
         <v>0</v>
       </c>
       <c r="K11" s="35" t="n">
-        <v>0.0325</v>
+        <v>0</v>
       </c>
       <c r="L11" s="36">
         <f>IF($H$4="-",0,IF($H$4="VAREJO",AW11,IF($H$4="ATACADO",AX11,0)))</f>
@@ -10295,12 +10291,12 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
+    <row r="12">
       <c r="A12" s="32" t="n">
         <v>2</v>
       </c>
       <c r="B12" s="33" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C12" s="33" t="inlineStr">
         <is>
@@ -10309,7 +10305,7 @@
       </c>
       <c r="D12" s="33" t="inlineStr">
         <is>
-          <t>010 DIFUSOR ALS DS2 1500 C/ CAIXA PLENUM PH4 TROX</t>
+          <t>010 DAMPER JN-B 0 800x800 00 000 TROX</t>
         </is>
       </c>
       <c r="E12" s="33" t="inlineStr">
@@ -10323,20 +10319,20 @@
       </c>
       <c r="G12" s="33" t="inlineStr">
         <is>
-          <t>ALS-DS2-1500/K/C/198/0/PH4</t>
+          <t>JN-B-0-D-N0/800x800/N/00/000</t>
         </is>
       </c>
       <c r="H12" s="33" t="n">
-        <v>76169900</v>
+        <v>90261029</v>
       </c>
       <c r="I12" s="46" t="n">
-        <v>456.37</v>
+        <v>770.28</v>
       </c>
       <c r="J12" s="35" t="n">
         <v>0</v>
       </c>
       <c r="K12" s="35" t="n">
-        <v>0.0325</v>
+        <v>0</v>
       </c>
       <c r="L12" s="36">
         <f>IF($H$4="-",0,IF($H$4="VAREJO",AW12,IF($H$4="ATACADO",AX12,0)))</f>
@@ -10426,7 +10422,7 @@
       </c>
       <c r="D13" s="33" t="inlineStr">
         <is>
-          <t>010 DIFUSOR ALS DS2 1500 C/ CAIXA PLENUM PH4 TROX</t>
+          <t>010 DAMPER JN-B 0 850x500 00 000 TROX</t>
         </is>
       </c>
       <c r="E13" s="33" t="inlineStr">
@@ -10440,20 +10436,20 @@
       </c>
       <c r="G13" s="33" t="inlineStr">
         <is>
-          <t>ALS-DS2-1500/K/B/198/0/PH4</t>
+          <t>JN-B-0-D-N0/850x500/N/00/000</t>
         </is>
       </c>
       <c r="H13" s="33" t="n">
-        <v>76169900</v>
+        <v>90261029</v>
       </c>
       <c r="I13" s="46" t="n">
-        <v>456.37</v>
+        <v>552.9</v>
       </c>
       <c r="J13" s="35" t="n">
         <v>0</v>
       </c>
       <c r="K13" s="35" t="n">
-        <v>0.0325</v>
+        <v>0</v>
       </c>
       <c r="L13" s="36">
         <f>IF($H$4="-",0,IF($H$4="VAREJO",AW13,IF($H$4="ATACADO",AX13,0)))</f>
@@ -10543,7 +10539,7 @@
       </c>
       <c r="D14" s="33" t="inlineStr">
         <is>
-          <t>010 CHAPA UNIAO - DIFUSOR ALS TROX</t>
+          <t>010 DAMPER JN-B 0 1200x600 00 000 TROX</t>
         </is>
       </c>
       <c r="E14" s="33" t="inlineStr">
@@ -10557,20 +10553,20 @@
       </c>
       <c r="G14" s="33" t="inlineStr">
         <is>
-          <t>CHAPA UNIAO - DIFUSOR ALS</t>
+          <t>JN-B-0-D-N0/1200x600/N/00/000</t>
         </is>
       </c>
       <c r="H14" s="33" t="n">
-        <v>73269090</v>
+        <v>90261029</v>
       </c>
       <c r="I14" s="46" t="n">
-        <v>4.23</v>
+        <v>758.47</v>
       </c>
       <c r="J14" s="35" t="n">
         <v>0</v>
       </c>
       <c r="K14" s="35" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="L14" s="36">
         <f>IF($H$4="-",0,IF($H$4="VAREJO",AW14,IF($H$4="ATACADO",AX14,0)))</f>
@@ -10651,7 +10647,7 @@
         <v>5</v>
       </c>
       <c r="B15" s="33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C15" s="33" t="inlineStr">
         <is>
@@ -10660,7 +10656,7 @@
       </c>
       <c r="D15" s="33" t="inlineStr">
         <is>
-          <t>010 PINO UNIAO - DIFUSOR ALS TROX</t>
+          <t>010 DAMPER JN-B 0 1800x400 00 000 TROX</t>
         </is>
       </c>
       <c r="E15" s="33" t="inlineStr">
@@ -10674,20 +10670,20 @@
       </c>
       <c r="G15" s="33" t="inlineStr">
         <is>
-          <t>PINO UNIAO - DIFUSOR ALS</t>
+          <t>JN-B-0-D-N0/1800x400/N/00/000</t>
         </is>
       </c>
       <c r="H15" s="33" t="n">
-        <v>73182400</v>
+        <v>90261029</v>
       </c>
       <c r="I15" s="46" t="n">
-        <v>2.21</v>
+        <v>742.95</v>
       </c>
       <c r="J15" s="35" t="n">
         <v>0</v>
       </c>
       <c r="K15" s="35" t="n">
-        <v>0.065</v>
+        <v>0</v>
       </c>
       <c r="L15" s="36">
         <f>IF($H$4="-",0,IF($H$4="VAREJO",AW15,IF($H$4="ATACADO",AX15,0)))</f>
@@ -10735,7 +10731,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="33" t="n">
-        <v>1</v>
+        <v>418</v>
       </c>
       <c r="C16" s="33" t="inlineStr">
         <is>
@@ -10744,7 +10740,7 @@
       </c>
       <c r="D16" s="33" t="inlineStr">
         <is>
-          <t>010 DIFUSOR ALS DS2 2000 C/ CAIXA PLENUM PH4 TROX</t>
+          <t>010 DIFUSOR ADLR T1 A PP5 TROX</t>
         </is>
       </c>
       <c r="E16" s="33" t="inlineStr">
@@ -10758,14 +10754,14 @@
       </c>
       <c r="G16" s="33" t="inlineStr">
         <is>
-          <t>ALS-DS2-2000/K/A/198/0/PH4</t>
+          <t>ADLR-A-000-0/T1/0/PP5</t>
         </is>
       </c>
       <c r="H16" s="33" t="n">
         <v>76169900</v>
       </c>
       <c r="I16" s="46" t="n">
-        <v>595.02</v>
+        <v>105.04</v>
       </c>
       <c r="J16" s="35" t="n">
         <v>0</v>
@@ -10818,45 +10814,23 @@
       <c r="A17" s="32" t="n">
         <v>7</v>
       </c>
-      <c r="B17" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="33" t="inlineStr">
-        <is>
-          <t>PÇ</t>
-        </is>
-      </c>
-      <c r="D17" s="33" t="inlineStr">
-        <is>
-          <t>010 DIFUSOR ALS DS2 1500 C/ CAIXA PLENUM PH4 TROX</t>
-        </is>
-      </c>
+      <c r="B17" s="33" t="n"/>
+      <c r="C17" s="33" t="n"/>
+      <c r="D17" s="33" t="n"/>
       <c r="E17" s="33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F17" s="54">
         <f>IFERROR((VLOOKUP(E17,$AE$11:$AG$14,3,0)),"-")</f>
         <v/>
       </c>
-      <c r="G17" s="33" t="inlineStr">
-        <is>
-          <t>ALS-DS2-1500/K/C/198/0/PH4</t>
-        </is>
-      </c>
-      <c r="H17" s="33" t="n">
-        <v>76169900</v>
-      </c>
-      <c r="I17" s="46" t="n">
-        <v>456.37</v>
-      </c>
-      <c r="J17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="35" t="n">
-        <v>0.0325</v>
-      </c>
+      <c r="G17" s="33" t="n"/>
+      <c r="H17" s="33" t="n"/>
+      <c r="I17" s="46" t="n"/>
+      <c r="J17" s="35" t="n"/>
+      <c r="K17" s="35" t="n"/>
       <c r="L17" s="36">
         <f>IF($H$4="-",0,IF($H$4="VAREJO",AW17,IF($H$4="ATACADO",AX17,0)))</f>
         <v/>
@@ -10902,45 +10876,23 @@
       <c r="A18" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="B18" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" s="33" t="inlineStr">
-        <is>
-          <t>PÇ</t>
-        </is>
-      </c>
-      <c r="D18" s="33" t="inlineStr">
-        <is>
-          <t>010 DIFUSOR ALS DS2 1500 C/ CAIXA PLENUM PH4 TROX</t>
-        </is>
-      </c>
+      <c r="B18" s="33" t="n"/>
+      <c r="C18" s="33" t="n"/>
+      <c r="D18" s="33" t="n"/>
       <c r="E18" s="33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F18" s="54">
         <f>IFERROR((VLOOKUP(E18,$AE$11:$AG$14,3,0)),"-")</f>
         <v/>
       </c>
-      <c r="G18" s="33" t="inlineStr">
-        <is>
-          <t>ALS-DS2-1500/K/B/198/0/PH4</t>
-        </is>
-      </c>
-      <c r="H18" s="33" t="n">
-        <v>76169900</v>
-      </c>
-      <c r="I18" s="46" t="n">
-        <v>456.37</v>
-      </c>
-      <c r="J18" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="35" t="n">
-        <v>0.0325</v>
-      </c>
+      <c r="G18" s="33" t="n"/>
+      <c r="H18" s="33" t="n"/>
+      <c r="I18" s="46" t="n"/>
+      <c r="J18" s="35" t="n"/>
+      <c r="K18" s="35" t="n"/>
       <c r="L18" s="36">
         <f>IF($H$4="-",0,IF($H$4="VAREJO",AW18,IF($H$4="ATACADO",AX18,0)))</f>
         <v/>
@@ -10986,45 +10938,23 @@
       <c r="A19" s="32" t="n">
         <v>9</v>
       </c>
-      <c r="B19" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="C19" s="33" t="inlineStr">
-        <is>
-          <t>PÇ</t>
-        </is>
-      </c>
-      <c r="D19" s="33" t="inlineStr">
-        <is>
-          <t>010 CHAPA UNIAO - DIFUSOR ALS TROX</t>
-        </is>
-      </c>
+      <c r="B19" s="33" t="n"/>
+      <c r="C19" s="33" t="n"/>
+      <c r="D19" s="33" t="n"/>
       <c r="E19" s="33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F19" s="54">
         <f>IFERROR((VLOOKUP(E19,$AE$11:$AG$14,3,0)),"-")</f>
         <v/>
       </c>
-      <c r="G19" s="33" t="inlineStr">
-        <is>
-          <t>CHAPA UNIAO - DIFUSOR ALS</t>
-        </is>
-      </c>
-      <c r="H19" s="33" t="n">
-        <v>73269090</v>
-      </c>
-      <c r="I19" s="46" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="J19" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="35" t="n">
-        <v>0.05</v>
-      </c>
+      <c r="G19" s="33" t="n"/>
+      <c r="H19" s="33" t="n"/>
+      <c r="I19" s="46" t="n"/>
+      <c r="J19" s="35" t="n"/>
+      <c r="K19" s="35" t="n"/>
       <c r="L19" s="36">
         <f>IF($H$4="-",0,IF($H$4="VAREJO",AW19,IF($H$4="ATACADO",AX19,0)))</f>
         <v/>
@@ -11070,45 +11000,23 @@
       <c r="A20" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="B20" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="C20" s="33" t="inlineStr">
-        <is>
-          <t>PÇ</t>
-        </is>
-      </c>
-      <c r="D20" s="33" t="inlineStr">
-        <is>
-          <t>010 PINO UNIAO - DIFUSOR ALS TROX</t>
-        </is>
-      </c>
+      <c r="B20" s="33" t="n"/>
+      <c r="C20" s="33" t="n"/>
+      <c r="D20" s="33" t="n"/>
       <c r="E20" s="33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F20" s="54">
         <f>IFERROR((VLOOKUP(E20,$AE$11:$AG$14,3,0)),"-")</f>
         <v/>
       </c>
-      <c r="G20" s="33" t="inlineStr">
-        <is>
-          <t>PINO UNIAO - DIFUSOR ALS</t>
-        </is>
-      </c>
-      <c r="H20" s="33" t="n">
-        <v>73182400</v>
-      </c>
-      <c r="I20" s="46" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="J20" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="35" t="n">
-        <v>0.065</v>
-      </c>
+      <c r="G20" s="33" t="n"/>
+      <c r="H20" s="33" t="n"/>
+      <c r="I20" s="46" t="n"/>
+      <c r="J20" s="35" t="n"/>
+      <c r="K20" s="35" t="n"/>
       <c r="L20" s="36">
         <f>IF($H$4="-",0,IF($H$4="VAREJO",AW20,IF($H$4="ATACADO",AX20,0)))</f>
         <v/>
@@ -11154,45 +11062,23 @@
       <c r="A21" s="32" t="n">
         <v>11</v>
       </c>
-      <c r="B21" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" s="33" t="inlineStr">
-        <is>
-          <t>PÇ</t>
-        </is>
-      </c>
-      <c r="D21" s="33" t="inlineStr">
-        <is>
-          <t>010 DIFUSOR ALS DS2 2000 C/ CAIXA PLENUM PH4 TROX</t>
-        </is>
-      </c>
+      <c r="B21" s="33" t="n"/>
+      <c r="C21" s="33" t="n"/>
+      <c r="D21" s="33" t="n"/>
       <c r="E21" s="33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F21" s="54">
         <f>IFERROR((VLOOKUP(E21,$AE$11:$AG$14,3,0)),"-")</f>
         <v/>
       </c>
-      <c r="G21" s="33" t="inlineStr">
-        <is>
-          <t>ALS-DS2-2000/K/C/198/0/PH4</t>
-        </is>
-      </c>
-      <c r="H21" s="33" t="n">
-        <v>76169900</v>
-      </c>
-      <c r="I21" s="46" t="n">
-        <v>579.11</v>
-      </c>
-      <c r="J21" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="35" t="n">
-        <v>0.0325</v>
-      </c>
+      <c r="G21" s="33" t="n"/>
+      <c r="H21" s="33" t="n"/>
+      <c r="I21" s="46" t="n"/>
+      <c r="J21" s="35" t="n"/>
+      <c r="K21" s="35" t="n"/>
       <c r="L21" s="36">
         <f>IF($H$4="-",0,IF($H$4="VAREJO",AW21,IF($H$4="ATACADO",AX21,0)))</f>
         <v/>
@@ -11238,45 +11124,23 @@
       <c r="A22" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="B22" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="33" t="inlineStr">
-        <is>
-          <t>PÇ</t>
-        </is>
-      </c>
-      <c r="D22" s="33" t="inlineStr">
-        <is>
-          <t>010 DIFUSOR ALS DS2 2000 C/ CAIXA PLENUM PH4 TROX</t>
-        </is>
-      </c>
+      <c r="B22" s="33" t="n"/>
+      <c r="C22" s="33" t="n"/>
+      <c r="D22" s="33" t="n"/>
       <c r="E22" s="33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F22" s="54">
         <f>IFERROR((VLOOKUP(E22,$AE$11:$AG$14,3,0)),"-")</f>
         <v/>
       </c>
-      <c r="G22" s="33" t="inlineStr">
-        <is>
-          <t>ALS-DS2-2000/K/B/198/0/PH4</t>
-        </is>
-      </c>
-      <c r="H22" s="33" t="n">
-        <v>76169900</v>
-      </c>
-      <c r="I22" s="46" t="n">
-        <v>579.11</v>
-      </c>
-      <c r="J22" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="35" t="n">
-        <v>0.0325</v>
-      </c>
+      <c r="G22" s="33" t="n"/>
+      <c r="H22" s="33" t="n"/>
+      <c r="I22" s="46" t="n"/>
+      <c r="J22" s="35" t="n"/>
+      <c r="K22" s="35" t="n"/>
       <c r="L22" s="36">
         <f>IF($H$4="-",0,IF($H$4="VAREJO",AW22,IF($H$4="ATACADO",AX22,0)))</f>
         <v/>
@@ -11322,45 +11186,23 @@
       <c r="A23" s="32" t="n">
         <v>13</v>
       </c>
-      <c r="B23" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="C23" s="33" t="inlineStr">
-        <is>
-          <t>PÇ</t>
-        </is>
-      </c>
-      <c r="D23" s="33" t="inlineStr">
-        <is>
-          <t>010 CHAPA UNIAO - DIFUSOR ALS TROX</t>
-        </is>
-      </c>
+      <c r="B23" s="33" t="n"/>
+      <c r="C23" s="33" t="n"/>
+      <c r="D23" s="33" t="n"/>
       <c r="E23" s="33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F23" s="54">
         <f>IFERROR((VLOOKUP(E23,$AE$11:$AG$14,3,0)),"-")</f>
         <v/>
       </c>
-      <c r="G23" s="33" t="inlineStr">
-        <is>
-          <t>CHAPA UNIAO - DIFUSOR ALS</t>
-        </is>
-      </c>
-      <c r="H23" s="33" t="n">
-        <v>73269090</v>
-      </c>
-      <c r="I23" s="46" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="J23" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="35" t="n">
-        <v>0.05</v>
-      </c>
+      <c r="G23" s="33" t="n"/>
+      <c r="H23" s="33" t="n"/>
+      <c r="I23" s="46" t="n"/>
+      <c r="J23" s="35" t="n"/>
+      <c r="K23" s="35" t="n"/>
       <c r="L23" s="36">
         <f>IF($H$4="-",0,IF($H$4="VAREJO",AW23,IF($H$4="ATACADO",AX23,0)))</f>
         <v/>
@@ -11406,45 +11248,23 @@
       <c r="A24" s="32" t="n">
         <v>14</v>
       </c>
-      <c r="B24" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="C24" s="33" t="inlineStr">
-        <is>
-          <t>PÇ</t>
-        </is>
-      </c>
-      <c r="D24" s="33" t="inlineStr">
-        <is>
-          <t>010 PINO UNIAO - DIFUSOR ALS TROX</t>
-        </is>
-      </c>
+      <c r="B24" s="33" t="n"/>
+      <c r="C24" s="33" t="n"/>
+      <c r="D24" s="33" t="n"/>
       <c r="E24" s="33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F24" s="54">
         <f>IFERROR((VLOOKUP(E24,$AE$11:$AG$14,3,0)),"-")</f>
         <v/>
       </c>
-      <c r="G24" s="33" t="inlineStr">
-        <is>
-          <t>PINO UNIAO - DIFUSOR ALS</t>
-        </is>
-      </c>
-      <c r="H24" s="33" t="n">
-        <v>73182400</v>
-      </c>
-      <c r="I24" s="46" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="J24" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="35" t="n">
-        <v>0.065</v>
-      </c>
+      <c r="G24" s="33" t="n"/>
+      <c r="H24" s="33" t="n"/>
+      <c r="I24" s="46" t="n"/>
+      <c r="J24" s="35" t="n"/>
+      <c r="K24" s="35" t="n"/>
       <c r="L24" s="36">
         <f>IF($H$4="-",0,IF($H$4="VAREJO",AW24,IF($H$4="ATACADO",AX24,0)))</f>
         <v/>
@@ -11490,45 +11310,23 @@
       <c r="A25" s="32" t="n">
         <v>15</v>
       </c>
-      <c r="B25" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="33" t="inlineStr">
-        <is>
-          <t>PÇ</t>
-        </is>
-      </c>
-      <c r="D25" s="33" t="inlineStr">
-        <is>
-          <t>010 DIFUSOR ALS DS2 2000 C/ CAIXA PLENUM PH4 TROX</t>
-        </is>
-      </c>
+      <c r="B25" s="33" t="n"/>
+      <c r="C25" s="33" t="n"/>
+      <c r="D25" s="33" t="n"/>
       <c r="E25" s="33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F25" s="54">
         <f>IFERROR((VLOOKUP(E25,$AE$11:$AG$14,3,0)),"-")</f>
         <v/>
       </c>
-      <c r="G25" s="33" t="inlineStr">
-        <is>
-          <t>ALS-DS2-2000/K/A/198/0/PH4</t>
-        </is>
-      </c>
-      <c r="H25" s="33" t="n">
-        <v>76169900</v>
-      </c>
-      <c r="I25" s="46" t="n">
-        <v>595.02</v>
-      </c>
-      <c r="J25" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="35" t="n">
-        <v>0.0325</v>
-      </c>
+      <c r="G25" s="33" t="n"/>
+      <c r="H25" s="33" t="n"/>
+      <c r="I25" s="46" t="n"/>
+      <c r="J25" s="35" t="n"/>
+      <c r="K25" s="35" t="n"/>
       <c r="L25" s="36">
         <f>IF($H$4="-",0,IF($H$4="VAREJO",AW25,IF($H$4="ATACADO",AX25,0)))</f>
         <v/>
@@ -11574,45 +11372,23 @@
       <c r="A26" s="32" t="n">
         <v>16</v>
       </c>
-      <c r="B26" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="33" t="inlineStr">
-        <is>
-          <t>PÇ</t>
-        </is>
-      </c>
-      <c r="D26" s="33" t="inlineStr">
-        <is>
-          <t>010 DIFUSOR ALS DS2 1500 C/ CAIXA PLENUM PH4 TROX</t>
-        </is>
-      </c>
+      <c r="B26" s="33" t="n"/>
+      <c r="C26" s="33" t="n"/>
+      <c r="D26" s="33" t="n"/>
       <c r="E26" s="33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F26" s="54">
         <f>IFERROR((VLOOKUP(E26,$AE$11:$AG$14,3,0)),"-")</f>
         <v/>
       </c>
-      <c r="G26" s="33" t="inlineStr">
-        <is>
-          <t>ALS-DS2-1500/K/C/198/0/PH4</t>
-        </is>
-      </c>
-      <c r="H26" s="33" t="n">
-        <v>76169900</v>
-      </c>
-      <c r="I26" s="46" t="n">
-        <v>456.37</v>
-      </c>
-      <c r="J26" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="35" t="n">
-        <v>0.0325</v>
-      </c>
+      <c r="G26" s="33" t="n"/>
+      <c r="H26" s="33" t="n"/>
+      <c r="I26" s="46" t="n"/>
+      <c r="J26" s="35" t="n"/>
+      <c r="K26" s="35" t="n"/>
       <c r="L26" s="36">
         <f>IF($H$4="-",0,IF($H$4="VAREJO",AW26,IF($H$4="ATACADO",AX26,0)))</f>
         <v/>
@@ -11658,45 +11434,23 @@
       <c r="A27" s="32" t="n">
         <v>17</v>
       </c>
-      <c r="B27" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="33" t="inlineStr">
-        <is>
-          <t>PÇ</t>
-        </is>
-      </c>
-      <c r="D27" s="33" t="inlineStr">
-        <is>
-          <t>010 DIFUSOR ALS DS2 1500 C/ CAIXA PLENUM PH4 TROX</t>
-        </is>
-      </c>
+      <c r="B27" s="33" t="n"/>
+      <c r="C27" s="33" t="n"/>
+      <c r="D27" s="33" t="n"/>
       <c r="E27" s="33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F27" s="54">
         <f>IFERROR((VLOOKUP(E27,$AE$11:$AG$14,3,0)),"-")</f>
         <v/>
       </c>
-      <c r="G27" s="33" t="inlineStr">
-        <is>
-          <t>ALS-DS2-1500/K/B/198/0/PH4</t>
-        </is>
-      </c>
-      <c r="H27" s="33" t="n">
-        <v>76169900</v>
-      </c>
-      <c r="I27" s="46" t="n">
-        <v>456.37</v>
-      </c>
-      <c r="J27" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="35" t="n">
-        <v>0.0325</v>
-      </c>
+      <c r="G27" s="33" t="n"/>
+      <c r="H27" s="33" t="n"/>
+      <c r="I27" s="46" t="n"/>
+      <c r="J27" s="35" t="n"/>
+      <c r="K27" s="35" t="n"/>
       <c r="L27" s="36">
         <f>IF($H$4="-",0,IF($H$4="VAREJO",AW27,IF($H$4="ATACADO",AX27,0)))</f>
         <v/>
@@ -11742,45 +11496,23 @@
       <c r="A28" s="32" t="n">
         <v>18</v>
       </c>
-      <c r="B28" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="C28" s="33" t="inlineStr">
-        <is>
-          <t>PÇ</t>
-        </is>
-      </c>
-      <c r="D28" s="33" t="inlineStr">
-        <is>
-          <t>010 CHAPA UNIAO - DIFUSOR ALS TROX</t>
-        </is>
-      </c>
+      <c r="B28" s="33" t="n"/>
+      <c r="C28" s="33" t="n"/>
+      <c r="D28" s="33" t="n"/>
       <c r="E28" s="33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F28" s="54">
         <f>IFERROR((VLOOKUP(E28,$AE$11:$AG$14,3,0)),"-")</f>
         <v/>
       </c>
-      <c r="G28" s="33" t="inlineStr">
-        <is>
-          <t>CHAPA UNIAO - DIFUSOR ALS</t>
-        </is>
-      </c>
-      <c r="H28" s="33" t="n">
-        <v>73269090</v>
-      </c>
-      <c r="I28" s="46" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="J28" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="35" t="n">
-        <v>0.05</v>
-      </c>
+      <c r="G28" s="33" t="n"/>
+      <c r="H28" s="33" t="n"/>
+      <c r="I28" s="46" t="n"/>
+      <c r="J28" s="35" t="n"/>
+      <c r="K28" s="35" t="n"/>
       <c r="L28" s="36">
         <f>IF($H$4="-",0,IF($H$4="VAREJO",AW28,IF($H$4="ATACADO",AX28,0)))</f>
         <v/>
@@ -11826,45 +11558,23 @@
       <c r="A29" s="32" t="n">
         <v>19</v>
       </c>
-      <c r="B29" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="C29" s="33" t="inlineStr">
-        <is>
-          <t>PÇ</t>
-        </is>
-      </c>
-      <c r="D29" s="33" t="inlineStr">
-        <is>
-          <t>010 PINO UNIAO - DIFUSOR ALS TROX</t>
-        </is>
-      </c>
+      <c r="B29" s="33" t="n"/>
+      <c r="C29" s="33" t="n"/>
+      <c r="D29" s="33" t="n"/>
       <c r="E29" s="33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F29" s="54">
         <f>IFERROR((VLOOKUP(E29,$AE$11:$AG$14,3,0)),"-")</f>
         <v/>
       </c>
-      <c r="G29" s="33" t="inlineStr">
-        <is>
-          <t>PINO UNIAO - DIFUSOR ALS</t>
-        </is>
-      </c>
-      <c r="H29" s="33" t="n">
-        <v>73182400</v>
-      </c>
-      <c r="I29" s="46" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="J29" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="35" t="n">
-        <v>0.065</v>
-      </c>
+      <c r="G29" s="33" t="n"/>
+      <c r="H29" s="33" t="n"/>
+      <c r="I29" s="46" t="n"/>
+      <c r="J29" s="35" t="n"/>
+      <c r="K29" s="35" t="n"/>
       <c r="L29" s="36">
         <f>IF($H$4="-",0,IF($H$4="VAREJO",AW29,IF($H$4="ATACADO",AX29,0)))</f>
         <v/>
@@ -11915,7 +11625,7 @@
       <c r="D30" s="33" t="n"/>
       <c r="E30" s="33" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F30" s="54">
@@ -11924,15 +11634,9 @@
       </c>
       <c r="G30" s="33" t="n"/>
       <c r="H30" s="33" t="n"/>
-      <c r="I30" s="46" t="n">
-        <v>2090</v>
-      </c>
-      <c r="J30" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="35" t="n">
-        <v>0</v>
-      </c>
+      <c r="I30" s="46" t="n"/>
+      <c r="J30" s="35" t="n"/>
+      <c r="K30" s="35" t="n"/>
       <c r="L30" s="36">
         <f>IF($H$4="-",0,IF($H$4="VAREJO",AW30,IF($H$4="ATACADO",AX30,0)))</f>
         <v/>
@@ -41740,9 +41444,9 @@
   <mergeCells count="14">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="K3:L4"/>
+    <mergeCell ref="H3:I3"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C4:D4"/>
     <mergeCell ref="K5:L5"/>
     <mergeCell ref="D1:M1"/>
     <mergeCell ref="H4:I4"/>
@@ -41751,7 +41455,7 @@
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C8:D8"/>
-    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="C4:D4"/>
   </mergeCells>
   <pageMargins left="0.7480314960629921" right="0.5118110236220472" top="0.7874015748031497" bottom="0.7874015748031497" header="0.3149606299212598" footer="0.3149606299212598"/>
   <pageSetup orientation="landscape" paperSize="9" scale="34" fitToHeight="0" blackAndWhite="1"/>
@@ -41767,25 +41471,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X510"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col width="9.7109375" customWidth="1" style="63" min="1" max="1"/>
-    <col width="15.140625" customWidth="1" style="63" min="2" max="2"/>
-    <col width="16.7109375" customWidth="1" style="63" min="3" max="3"/>
+    <col width="9.6640625" customWidth="1" style="63" min="1" max="1"/>
+    <col width="15.109375" customWidth="1" style="63" min="2" max="2"/>
+    <col width="16.6640625" customWidth="1" style="63" min="3" max="3"/>
     <col width="56" customWidth="1" style="62" min="4" max="4"/>
-    <col width="34.28515625" customWidth="1" style="62" min="5" max="5"/>
-    <col width="17.7109375" customWidth="1" style="62" min="6" max="6"/>
-    <col width="24.5703125" customWidth="1" style="62" min="7" max="8"/>
-    <col width="45.5703125" customWidth="1" style="62" min="9" max="9"/>
-    <col width="1.5703125" customWidth="1" style="62" min="10" max="10"/>
-    <col width="19.28515625" customWidth="1" style="62" min="11" max="11"/>
-    <col width="9.140625" customWidth="1" style="62" min="12" max="16384"/>
+    <col width="34.33203125" customWidth="1" style="62" min="5" max="5"/>
+    <col width="17.6640625" customWidth="1" style="62" min="6" max="6"/>
+    <col width="24.5546875" customWidth="1" style="62" min="7" max="8"/>
+    <col width="45.5546875" customWidth="1" style="62" min="9" max="9"/>
+    <col width="1.5546875" customWidth="1" style="62" min="10" max="10"/>
+    <col width="19.33203125" customWidth="1" style="62" min="11" max="11"/>
+    <col width="9.109375" customWidth="1" style="62" min="12" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="62.25" customHeight="1">
-      <c r="A1" s="101" t="n"/>
+      <c r="A1" s="98" t="n"/>
       <c r="B1" s="107" t="n"/>
-      <c r="C1" s="106">
+      <c r="C1" s="104">
         <f>CONCATENATE("CTD ",C5," - Rev. ",C6," - ",C8," - ",C4)</f>
         <v/>
       </c>
@@ -41800,26 +41504,26 @@
       <c r="C2" s="64" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="100" t="inlineStr">
+      <c r="A3" s="106" t="inlineStr">
         <is>
           <t>Orçamentista:</t>
         </is>
       </c>
       <c r="B3" s="120" t="n"/>
-      <c r="C3" s="98">
+      <c r="C3" s="102">
         <f>'COMPOSIÇÃO DE VALORES'!C3</f>
         <v/>
       </c>
       <c r="D3" s="108" t="n"/>
       <c r="E3" s="66" t="n"/>
-      <c r="F3" s="103" t="inlineStr">
+      <c r="F3" s="100" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
       <c r="G3" s="108" t="n"/>
       <c r="H3" s="68" t="n"/>
-      <c r="I3" s="103" t="inlineStr">
+      <c r="I3" s="100" t="inlineStr">
         <is>
           <t>Soma Total</t>
         </is>
@@ -41827,19 +41531,19 @@
       <c r="J3" s="69" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="100" t="inlineStr">
+      <c r="A4" s="106" t="inlineStr">
         <is>
           <t>Vendedor(a):</t>
         </is>
       </c>
       <c r="B4" s="120" t="n"/>
-      <c r="C4" s="98">
+      <c r="C4" s="102">
         <f>'COMPOSIÇÃO DE VALORES'!C4</f>
         <v/>
       </c>
       <c r="D4" s="108" t="n"/>
       <c r="E4" s="66" t="n"/>
-      <c r="F4" s="104">
+      <c r="F4" s="101">
         <f>W4</f>
         <v/>
       </c>
@@ -41859,7 +41563,7 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="100" t="inlineStr">
+      <c r="A5" s="106" t="inlineStr">
         <is>
           <t>Nº CTD:</t>
         </is>
@@ -41878,7 +41582,7 @@
       <c r="X5" s="73" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="100" t="inlineStr">
+      <c r="A6" s="106" t="inlineStr">
         <is>
           <t>Revisão:</t>
         </is>
@@ -41897,8 +41601,8 @@
       <c r="X6" s="73" t="n"/>
     </row>
     <row r="7" ht="4.5" customHeight="1">
-      <c r="A7" s="99" t="n"/>
-      <c r="B7" s="99" t="n"/>
+      <c r="A7" s="105" t="n"/>
+      <c r="B7" s="105" t="n"/>
       <c r="D7" s="76" t="n"/>
       <c r="E7" s="66" t="n"/>
       <c r="F7" s="75" t="n"/>
@@ -41907,13 +41611,13 @@
       <c r="I7" s="70" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="100" t="inlineStr">
+      <c r="A8" s="106" t="inlineStr">
         <is>
           <t>Fabricante:</t>
         </is>
       </c>
       <c r="B8" s="120" t="n"/>
-      <c r="C8" s="98">
+      <c r="C8" s="102">
         <f>'COMPOSIÇÃO DE VALORES'!C8</f>
         <v/>
       </c>
@@ -41924,7 +41628,7 @@
       <c r="H8" s="70" t="n"/>
       <c r="I8" s="70" t="n"/>
     </row>
-    <row r="9" ht="10.9" customHeight="1">
+    <row r="9" ht="10.95" customHeight="1">
       <c r="D9" s="77" t="n"/>
     </row>
     <row r="10" ht="34.5" customFormat="1" customHeight="1" s="75">
@@ -41972,7 +41676,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="1">
       <c r="A11" s="81" t="n">
         <v>1</v>
       </c>
@@ -42009,7 +41713,7 @@
         <v/>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="1">
       <c r="A12" s="81" t="n">
         <v>2</v>
       </c>
@@ -42046,7 +41750,7 @@
         <v/>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="1">
       <c r="A13" s="81" t="n">
         <v>3</v>
       </c>
@@ -42083,7 +41787,7 @@
         <v/>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="1">
       <c r="A14" s="81" t="n">
         <v>4</v>
       </c>
@@ -60484,14 +60188,14 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="12">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F4:G4"/>
     <mergeCell ref="F3:G3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C3:D3"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C3:D3"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C8:D8"/>

--- a/PlanDist.xlsx
+++ b/PlanDist.xlsx
@@ -9892,7 +9892,7 @@
       <c r="B3" s="112" t="n"/>
       <c r="C3" s="113" t="inlineStr">
         <is>
-          <t>Luiz Henrique</t>
+          <t>Felipe Almeida</t>
         </is>
       </c>
       <c r="D3" s="114" t="n"/>
@@ -9922,7 +9922,7 @@
       <c r="B4" s="112" t="n"/>
       <c r="C4" s="113" t="inlineStr">
         <is>
-          <t>Iago Rangel</t>
+          <t>Wellisson Chaves</t>
         </is>
       </c>
       <c r="D4" s="114" t="n"/>
@@ -9948,7 +9948,7 @@
       <c r="B5" s="112" t="n"/>
       <c r="C5" s="59" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1121</t>
         </is>
       </c>
       <c r="E5" s="21" t="n"/>
@@ -9971,7 +9971,11 @@
         </is>
       </c>
       <c r="B6" s="112" t="n"/>
-      <c r="C6" s="58" t="inlineStr"/>
+      <c r="C6" s="58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="E6" s="50" t="n"/>
       <c r="F6" s="21" t="n"/>
       <c r="G6" s="22" t="n"/>
@@ -10179,7 +10183,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="33" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C11" s="33" t="inlineStr">
         <is>
@@ -10188,7 +10192,7 @@
       </c>
       <c r="D11" s="33" t="inlineStr">
         <is>
-          <t>010 DAMPER RG-B 480x405 TROX</t>
+          <t>010 DAMPER JN-B 0 1050x550 00 000 TROX</t>
         </is>
       </c>
       <c r="E11" s="33" t="inlineStr">
@@ -10202,14 +10206,14 @@
       </c>
       <c r="G11" s="33" t="inlineStr">
         <is>
-          <t>RG-B-480x405/D/0/00/000</t>
+          <t>JN-B-0-D-N0/1050x550/N/00/000</t>
         </is>
       </c>
       <c r="H11" s="33" t="n">
         <v>90261029</v>
       </c>
       <c r="I11" s="34" t="n">
-        <v>176.23</v>
+        <v>660.9</v>
       </c>
       <c r="J11" s="35" t="n">
         <v>0</v>
@@ -10296,7 +10300,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="33" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C12" s="33" t="inlineStr">
         <is>
@@ -10305,7 +10309,7 @@
       </c>
       <c r="D12" s="33" t="inlineStr">
         <is>
-          <t>010 DAMPER JN-B 0 800x800 00 000 TROX</t>
+          <t>010 DAMPER JN-B 0 750x500 00 000 TROX</t>
         </is>
       </c>
       <c r="E12" s="33" t="inlineStr">
@@ -10319,14 +10323,14 @@
       </c>
       <c r="G12" s="33" t="inlineStr">
         <is>
-          <t>JN-B-0-D-N0/800x800/N/00/000</t>
+          <t>JN-B-0-D-N0/750x500/N/00/000</t>
         </is>
       </c>
       <c r="H12" s="33" t="n">
         <v>90261029</v>
       </c>
       <c r="I12" s="46" t="n">
-        <v>770.28</v>
+        <v>520.73</v>
       </c>
       <c r="J12" s="35" t="n">
         <v>0</v>
@@ -10413,7 +10417,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" s="33" t="inlineStr">
         <is>
@@ -10422,7 +10426,7 @@
       </c>
       <c r="D13" s="33" t="inlineStr">
         <is>
-          <t>010 DAMPER JN-B 0 850x500 00 000 TROX</t>
+          <t>010 DAMPER JN-B 0 1000x400 00 000 TROX</t>
         </is>
       </c>
       <c r="E13" s="33" t="inlineStr">
@@ -10436,14 +10440,14 @@
       </c>
       <c r="G13" s="33" t="inlineStr">
         <is>
-          <t>JN-B-0-D-N0/850x500/N/00/000</t>
+          <t>JN-B-0-D-N0/1000x400/N/00/000</t>
         </is>
       </c>
       <c r="H13" s="33" t="n">
         <v>90261029</v>
       </c>
       <c r="I13" s="46" t="n">
-        <v>552.9</v>
+        <v>515.79</v>
       </c>
       <c r="J13" s="35" t="n">
         <v>0</v>
@@ -10530,7 +10534,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" s="33" t="inlineStr">
         <is>
@@ -10539,7 +10543,7 @@
       </c>
       <c r="D14" s="33" t="inlineStr">
         <is>
-          <t>010 DAMPER JN-B 0 1200x600 00 000 TROX</t>
+          <t>010 GRELHA AR-A 825x225 AN0 TROX</t>
         </is>
       </c>
       <c r="E14" s="33" t="inlineStr">
@@ -10553,20 +10557,20 @@
       </c>
       <c r="G14" s="33" t="inlineStr">
         <is>
-          <t>JN-B-0-D-N0/1200x600/N/00/000</t>
+          <t>AR-A-825x225/0/0/FAN000</t>
         </is>
       </c>
       <c r="H14" s="33" t="n">
-        <v>90261029</v>
+        <v>76169900</v>
       </c>
       <c r="I14" s="46" t="n">
-        <v>758.47</v>
+        <v>120.23</v>
       </c>
       <c r="J14" s="35" t="n">
         <v>0</v>
       </c>
       <c r="K14" s="35" t="n">
-        <v>0</v>
+        <v>0.0325</v>
       </c>
       <c r="L14" s="36">
         <f>IF($H$4="-",0,IF($H$4="VAREJO",AW14,IF($H$4="ATACADO",AX14,0)))</f>
@@ -10646,45 +10650,23 @@
       <c r="A15" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="B15" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="33" t="inlineStr">
-        <is>
-          <t>PÇ</t>
-        </is>
-      </c>
-      <c r="D15" s="33" t="inlineStr">
-        <is>
-          <t>010 DAMPER JN-B 0 1800x400 00 000 TROX</t>
-        </is>
-      </c>
+      <c r="B15" s="33" t="n"/>
+      <c r="C15" s="33" t="n"/>
+      <c r="D15" s="33" t="n"/>
       <c r="E15" s="33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F15" s="54">
         <f>IFERROR((VLOOKUP(E15,$AE$11:$AG$14,3,0)),"-")</f>
         <v/>
       </c>
-      <c r="G15" s="33" t="inlineStr">
-        <is>
-          <t>JN-B-0-D-N0/1800x400/N/00/000</t>
-        </is>
-      </c>
-      <c r="H15" s="33" t="n">
-        <v>90261029</v>
-      </c>
-      <c r="I15" s="46" t="n">
-        <v>742.95</v>
-      </c>
-      <c r="J15" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="35" t="n">
-        <v>0</v>
-      </c>
+      <c r="G15" s="33" t="n"/>
+      <c r="H15" s="33" t="n"/>
+      <c r="I15" s="46" t="n"/>
+      <c r="J15" s="35" t="n"/>
+      <c r="K15" s="35" t="n"/>
       <c r="L15" s="36">
         <f>IF($H$4="-",0,IF($H$4="VAREJO",AW15,IF($H$4="ATACADO",AX15,0)))</f>
         <v/>
@@ -10730,45 +10712,23 @@
       <c r="A16" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="B16" s="33" t="n">
-        <v>418</v>
-      </c>
-      <c r="C16" s="33" t="inlineStr">
-        <is>
-          <t>PÇ</t>
-        </is>
-      </c>
-      <c r="D16" s="33" t="inlineStr">
-        <is>
-          <t>010 DIFUSOR ADLR T1 A PP5 TROX</t>
-        </is>
-      </c>
+      <c r="B16" s="33" t="n"/>
+      <c r="C16" s="33" t="n"/>
+      <c r="D16" s="33" t="n"/>
       <c r="E16" s="33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F16" s="54">
         <f>IFERROR((VLOOKUP(E16,$AE$11:$AG$14,3,0)),"-")</f>
         <v/>
       </c>
-      <c r="G16" s="33" t="inlineStr">
-        <is>
-          <t>ADLR-A-000-0/T1/0/PP5</t>
-        </is>
-      </c>
-      <c r="H16" s="33" t="n">
-        <v>76169900</v>
-      </c>
-      <c r="I16" s="46" t="n">
-        <v>105.04</v>
-      </c>
-      <c r="J16" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="35" t="n">
-        <v>0.0325</v>
-      </c>
+      <c r="G16" s="33" t="n"/>
+      <c r="H16" s="33" t="n"/>
+      <c r="I16" s="46" t="n"/>
+      <c r="J16" s="35" t="n"/>
+      <c r="K16" s="35" t="n"/>
       <c r="L16" s="36">
         <f>IF($H$4="-",0,IF($H$4="VAREJO",AW16,IF($H$4="ATACADO",AX16,0)))</f>
         <v/>
